--- a/data/out/variants/v7_only_gen_enso_lags/raw_v7_only_gen_enso_lags.xlsx
+++ b/data/out/variants/v7_only_gen_enso_lags/raw_v7_only_gen_enso_lags.xlsx
@@ -550,7 +550,7 @@
         <v>9639</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02231502532958984</v>
+        <v>0.03609704971313477</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         <v>9639</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02201080322265625</v>
+        <v>0.02918791770935059</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>9639</v>
       </c>
       <c r="N4" t="n">
-        <v>0.08049821853637695</v>
+        <v>0.08431911468505859</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>9639</v>
       </c>
       <c r="N5" t="n">
-        <v>1.818623065948486</v>
+        <v>2.322342157363892</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>9639</v>
       </c>
       <c r="N6" t="n">
-        <v>5.530768871307373</v>
+        <v>7.081945896148682</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.1102014355671057</v>
+        <v>0.1102014355671058</v>
       </c>
       <c r="G7" t="n">
         <v>267.0974971988797</v>
       </c>
       <c r="H7" t="n">
-        <v>223599.0509299944</v>
+        <v>223599.0509299943</v>
       </c>
       <c r="I7" t="n">
-        <v>472.8626131658057</v>
+        <v>472.8626131658056</v>
       </c>
       <c r="J7" t="n">
         <v>55.97387097910575</v>
@@ -836,7 +836,7 @@
         <v>9639</v>
       </c>
       <c r="N7" t="n">
-        <v>774.6748921871185</v>
+        <v>855.1002440452576</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>9639</v>
       </c>
       <c r="N8" t="n">
-        <v>394.881370306015</v>
+        <v>422.42640209198</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>9639</v>
       </c>
       <c r="N9" t="n">
-        <v>238.6711513996124</v>
+        <v>264.6536192893982</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>9639</v>
       </c>
       <c r="N10" t="n">
-        <v>0.956251859664917</v>
+        <v>1.078408002853394</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1048,23 +1048,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 699, 'learning_rate': 0.07938504169255677, 'max_depth': 3, 'subsample': 0.6574466329586887, 'colsample_bytree': 0.9988390722459425}</t>
+          <t>{'n_estimators': 740, 'learning_rate': 0.08410337003235431, 'max_depth': 3, 'subsample': 0.8775778785176162, 'colsample_bytree': 0.9546290105644548}</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.2521112762611912</v>
+        <v>0.2500891691309788</v>
       </c>
       <c r="G11" t="n">
-        <v>240.6561407661616</v>
+        <v>240.6082585920834</v>
       </c>
       <c r="H11" t="n">
-        <v>187938.2767220165</v>
+        <v>188446.4155899214</v>
       </c>
       <c r="I11" t="n">
-        <v>433.518484867735</v>
+        <v>434.1041529286738</v>
       </c>
       <c r="J11" t="n">
-        <v>46.30794547705905</v>
+        <v>46.58768886871046</v>
       </c>
       <c r="K11" t="n">
         <v>48192</v>
@@ -1076,7 +1076,7 @@
         <v>9639</v>
       </c>
       <c r="N11" t="n">
-        <v>88.97510504722595</v>
+        <v>91.58575844764709</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1106,23 +1106,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 365, 'learning_rate': 0.03856906735859017, 'num_leaves': 75, 'min_child_samples': 42}</t>
+          <t>{'n_estimators': 571, 'learning_rate': 0.01057499548945314, 'num_leaves': 116, 'min_child_samples': 50}</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.1703977547650317</v>
+        <v>0.171894365181951</v>
       </c>
       <c r="G12" t="n">
-        <v>249.9822015053584</v>
+        <v>250.9858020804327</v>
       </c>
       <c r="H12" t="n">
-        <v>208472.2116877735</v>
+        <v>208096.1258159691</v>
       </c>
       <c r="I12" t="n">
-        <v>456.5875728573583</v>
+        <v>456.1755427639332</v>
       </c>
       <c r="J12" t="n">
-        <v>48.80035869606847</v>
+        <v>49.91085540288407</v>
       </c>
       <c r="K12" t="n">
         <v>48192</v>
@@ -1134,7 +1134,7 @@
         <v>9639</v>
       </c>
       <c r="N12" t="n">
-        <v>324.1360638141632</v>
+        <v>446.7530715465546</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1164,23 +1164,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>{'iterations': 516, 'learning_rate': 0.06813869495565933, 'depth': 4}</t>
+          <t>{'iterations': 758, 'learning_rate': 0.054561703454024627, 'depth': 4}</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.1819967318618446</v>
+        <v>0.1878895578460893</v>
       </c>
       <c r="G13" t="n">
-        <v>251.2689505291841</v>
+        <v>250.3186429222821</v>
       </c>
       <c r="H13" t="n">
-        <v>205557.4842716205</v>
+        <v>204076.6656346378</v>
       </c>
       <c r="I13" t="n">
-        <v>453.3844773165713</v>
+        <v>451.748453937186</v>
       </c>
       <c r="J13" t="n">
-        <v>48.75141833390735</v>
+        <v>48.11724788096065</v>
       </c>
       <c r="K13" t="n">
         <v>48192</v>
@@ -1192,7 +1192,7 @@
         <v>9639</v>
       </c>
       <c r="N13" t="n">
-        <v>247.4920811653137</v>
+        <v>249.8411865234375</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>9639</v>
       </c>
       <c r="N14" t="n">
-        <v>124.9646954536438</v>
+        <v>122.856862783432</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>9639</v>
       </c>
       <c r="N15" t="n">
-        <v>31.92151856422424</v>
+        <v>26.37963247299194</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>9639</v>
       </c>
       <c r="N16" t="n">
-        <v>1646.041309356689</v>
+        <v>1565.413895606995</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
